--- a/backend/{templates}/carbon-credits.xlsx
+++ b/backend/{templates}/carbon-credits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{4007055A-7FB8-4884-B6C5-AD44DAA53F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28C234D8-0A93-4E01-8477-D5286C406B4D}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{4007055A-7FB8-4884-B6C5-AD44DAA53F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{291A6465-E46D-4C1D-97BD-64D5EC7CC2DB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -491,7 +491,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="59.54296875" customWidth="1"/>
-    <col min="2" max="3" width="22.54296875" customWidth="1"/>
+    <col min="2" max="2" width="22.54296875" customWidth="1"/>
+    <col min="3" max="3" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">

--- a/backend/{templates}/carbon-credits.xlsx
+++ b/backend/{templates}/carbon-credits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{4007055A-7FB8-4884-B6C5-AD44DAA53F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{291A6465-E46D-4C1D-97BD-64D5EC7CC2DB}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{4007055A-7FB8-4884-B6C5-AD44DAA53F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D197141-1F65-48C0-89B0-9F906D58182C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -221,6 +221,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -487,7 +491,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99682AE1-5334-4A99-9652-64DF807A4E7D}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:AS8"/>
+  <dimension ref="A1:AR8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="59.54296875" customWidth="1"/>
@@ -495,7 +499,7 @@
     <col min="3" max="3" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
@@ -506,131 +510,128 @@
         <v>8</v>
       </c>
       <c r="D1" s="7">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E1" s="7">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F1" s="7">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G1" s="7">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H1" s="7">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="I1" s="7">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="J1" s="7">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="K1" s="7">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="L1" s="7">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="M1" s="7">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="N1" s="7">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="O1" s="7">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="P1" s="7">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="Q1" s="7">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="R1" s="7">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="S1" s="7">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="T1" s="7">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="U1" s="7">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="V1" s="7">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="W1" s="7">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="X1" s="7">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="Y1" s="7">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="Z1" s="7">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="AA1" s="7">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="AB1" s="7">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="AC1" s="7">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="AD1" s="7">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="AE1" s="7">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="AF1" s="7">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="AG1" s="7">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="AH1" s="7">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="AI1" s="7">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="AJ1" s="7">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="AK1" s="7">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="AL1" s="7">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="AM1" s="7">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="AN1" s="7">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="AO1" s="7">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="AP1" s="7">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="AQ1" s="7">
-        <v>2059</v>
-      </c>
-      <c r="AR1" s="7">
         <v>2060</v>
       </c>
-      <c r="AS1" s="8"/>
+      <c r="AR1" s="8"/>
     </row>
-    <row r="2" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -760,12 +761,9 @@
       <c r="AQ2" s="11">
         <v>0</v>
       </c>
-      <c r="AR2" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS2" s="8"/>
+      <c r="AR2" s="8"/>
     </row>
-    <row r="3" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -895,12 +893,9 @@
       <c r="AQ3" s="11">
         <v>0</v>
       </c>
-      <c r="AR3" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS3" s="8"/>
+      <c r="AR3" s="8"/>
     </row>
-    <row r="4" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -1030,12 +1025,9 @@
       <c r="AQ4" s="11">
         <v>0</v>
       </c>
-      <c r="AR4" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS4" s="8"/>
+      <c r="AR4" s="8"/>
     </row>
-    <row r="5" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -1165,12 +1157,9 @@
       <c r="AQ5" s="11">
         <v>0</v>
       </c>
-      <c r="AR5" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS5" s="8"/>
+      <c r="AR5" s="8"/>
     </row>
-    <row r="6" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -1300,12 +1289,9 @@
       <c r="AQ6" s="11">
         <v>0</v>
       </c>
-      <c r="AR6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS6" s="8"/>
+      <c r="AR6" s="8"/>
     </row>
-    <row r="7" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="9"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1339,7 +1325,7 @@
       <c r="AE7" s="10"/>
       <c r="AF7" s="10"/>
       <c r="AG7" s="10"/>
-      <c r="AH7" s="10"/>
+      <c r="AH7" s="8"/>
       <c r="AI7" s="8"/>
       <c r="AJ7" s="8"/>
       <c r="AK7" s="8"/>
@@ -1350,9 +1336,8 @@
       <c r="AP7" s="8"/>
       <c r="AQ7" s="8"/>
       <c r="AR7" s="8"/>
-      <c r="AS7" s="8"/>
     </row>
-    <row r="8" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1367,7 +1352,6 @@
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
